--- a/data/dividends_info_20260602.xlsx
+++ b/data/dividends_info_20260602.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>65.55999755859375</v>
+        <v>68.27999877929688</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1372788336661593</v>
+        <v>0.1318101956781066</v>
       </c>
       <c r="J2" t="n">
         <v>286</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>55.20000076293945</v>
+        <v>54.54999923706055</v>
       </c>
       <c r="I3" t="n">
-        <v>1.26811592450189</v>
+        <v>1.283226415747462</v>
       </c>
       <c r="J3" t="n">
         <v>265</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9.100000381469727</v>
+        <v>9.260000228881836</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6593406317012648</v>
+        <v>0.6479481481313648</v>
       </c>
       <c r="J4" t="n">
         <v>195</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>65.55999755859375</v>
+        <v>68.27999877929688</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1372788336661593</v>
+        <v>0.1318101956781066</v>
       </c>
       <c r="J6" t="n">
         <v>195</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.119999885559082</v>
+        <v>2.105000019073486</v>
       </c>
       <c r="I7" t="n">
-        <v>3.632075667763242</v>
+        <v>3.65795721151069</v>
       </c>
       <c r="J7" t="n">
         <v>174</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>22.90999984741211</v>
+        <v>23.14500045776367</v>
       </c>
       <c r="I8" t="n">
-        <v>1.178524669569122</v>
+        <v>1.166558628904379</v>
       </c>
       <c r="J8" t="n">
         <v>174</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5.630000114440918</v>
+        <v>5.590000152587891</v>
       </c>
       <c r="I9" t="n">
-        <v>3.552397796351747</v>
+        <v>3.577817433643719</v>
       </c>
       <c r="J9" t="n">
         <v>167</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>7.25</v>
+        <v>7.300000190734863</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8275862068965517</v>
+        <v>0.8219177867440579</v>
       </c>
       <c r="J10" t="n">
         <v>139</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5.739999771118164</v>
+        <v>5.460000038146973</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8710801741070435</v>
+        <v>0.9157509093529076</v>
       </c>
       <c r="J12" t="n">
         <v>125</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>4.949999809265137</v>
+        <v>4.96999979019165</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7676767972571169</v>
+        <v>0.7645875574279384</v>
       </c>
       <c r="J13" t="n">
         <v>118</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>22.90999984741211</v>
+        <v>23.14500045776367</v>
       </c>
       <c r="I14" t="n">
-        <v>1.178524669569122</v>
+        <v>1.166558628904379</v>
       </c>
       <c r="J14" t="n">
         <v>111</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>65.55999755859375</v>
+        <v>68.27999877929688</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1372788336661593</v>
+        <v>0.1318101956781066</v>
       </c>
       <c r="J15" t="n">
         <v>111</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>5.940000057220459</v>
+        <v>5.900000095367432</v>
       </c>
       <c r="I16" t="n">
-        <v>5.050505001853162</v>
+        <v>5.08474568052218</v>
       </c>
       <c r="J16" t="n">
         <v>104</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>4.949999809265137</v>
+        <v>4.96999979019165</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7676767972571169</v>
+        <v>0.7645875574279384</v>
       </c>
       <c r="J18" t="n">
         <v>62</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>4.579999923706055</v>
+        <v>4.550000190734863</v>
       </c>
       <c r="I20" t="n">
-        <v>3.056768609871821</v>
+        <v>3.076922947939236</v>
       </c>
       <c r="J20" t="n">
         <v>48</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>9.602999687194824</v>
+        <v>9.576999664306641</v>
       </c>
       <c r="I21" t="n">
-        <v>2.70748733176258</v>
+        <v>2.714837726986843</v>
       </c>
       <c r="J21" t="n">
         <v>48</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>14.88000011444092</v>
+        <v>14.89999961853027</v>
       </c>
       <c r="I22" t="n">
-        <v>4.032258033504347</v>
+        <v>4.026845740679177</v>
       </c>
       <c r="J22" t="n">
         <v>48</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>3.75600004196167</v>
+        <v>3.664000034332275</v>
       </c>
       <c r="I23" t="n">
-        <v>5.857294929238052</v>
+        <v>6.004366755965182</v>
       </c>
       <c r="J23" t="n">
         <v>48</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>6.25</v>
+        <v>6.244999885559082</v>
       </c>
       <c r="I25" t="n">
-        <v>1.6</v>
+        <v>1.601281054163663</v>
       </c>
       <c r="J25" t="n">
         <v>48</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>2.640000104904175</v>
+        <v>2.700000047683716</v>
       </c>
       <c r="I29" t="n">
-        <v>5.681817956043021</v>
+        <v>5.555555457440915</v>
       </c>
       <c r="J29" t="n">
         <v>41</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>4.309999942779541</v>
+        <v>4.369999885559082</v>
       </c>
       <c r="I31" t="n">
-        <v>1.62412995195672</v>
+        <v>1.601830705564068</v>
       </c>
       <c r="J31" t="n">
         <v>34</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>33.5</v>
+        <v>32.40000152587891</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4477611940298508</v>
+        <v>0.4629629411597103</v>
       </c>
       <c r="J32" t="n">
         <v>34</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>22.31999969482422</v>
+        <v>22.47999954223633</v>
       </c>
       <c r="I34" t="n">
-        <v>1.120071699902274</v>
+        <v>1.112099666773969</v>
       </c>
       <c r="J34" t="n">
         <v>20</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>31.85000038146973</v>
+        <v>32.20000076293945</v>
       </c>
       <c r="I35" t="n">
-        <v>0.6122448906262828</v>
+        <v>0.6055900477630888</v>
       </c>
       <c r="J35" t="n">
         <v>20</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>5.255000114440918</v>
+        <v>5.309999942779541</v>
       </c>
       <c r="I37" t="n">
-        <v>5.518553638144938</v>
+        <v>5.461393655838691</v>
       </c>
       <c r="J37" t="n">
         <v>20</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>3.796000003814697</v>
+        <v>3.75</v>
       </c>
       <c r="I38" t="n">
-        <v>4.214963114836984</v>
+        <v>4.266666666666667</v>
       </c>
       <c r="J38" t="n">
         <v>20</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>2.628000020980835</v>
+        <v>2.630000114440918</v>
       </c>
       <c r="I39" t="n">
-        <v>5.273972560634571</v>
+        <v>5.269961747871004</v>
       </c>
       <c r="J39" t="n">
         <v>20</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>52.09999847412109</v>
+        <v>52.34000015258789</v>
       </c>
       <c r="I40" t="n">
-        <v>1.209213087238248</v>
+        <v>1.203668318997608</v>
       </c>
       <c r="J40" t="n">
         <v>20</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>5.934999942779541</v>
+        <v>5.929999828338623</v>
       </c>
       <c r="I41" t="n">
-        <v>2.358887975564727</v>
+        <v>2.360876965475783</v>
       </c>
       <c r="J41" t="n">
         <v>20</v>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>20</v>
+        <v>19.45000076293945</v>
       </c>
       <c r="I42" t="n">
-        <v>3.9</v>
+        <v>4.010282619043556</v>
       </c>
       <c r="J42" t="n">
         <v>20</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>25.64999961853027</v>
+        <v>25.69000053405762</v>
       </c>
       <c r="I43" t="n">
-        <v>3.313840205229229</v>
+        <v>3.308680351614404</v>
       </c>
       <c r="J43" t="n">
         <v>20</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>65.55999755859375</v>
+        <v>68.27999877929688</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1372788336661593</v>
+        <v>0.1318101956781066</v>
       </c>
       <c r="J44" t="n">
         <v>20</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1.460000038146973</v>
+        <v>1.470000028610229</v>
       </c>
       <c r="I45" t="n">
-        <v>0.6849314889533817</v>
+        <v>0.6802720956035777</v>
       </c>
       <c r="J45" t="n">
         <v>20</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>6.190000057220459</v>
+        <v>6.144000053405762</v>
       </c>
       <c r="I46" t="n">
-        <v>2.928917581971889</v>
+        <v>2.950846328516895</v>
       </c>
       <c r="J46" t="n">
         <v>20</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>9.100000381469727</v>
+        <v>8.939999580383301</v>
       </c>
       <c r="I47" t="n">
-        <v>2.857142737372147</v>
+        <v>2.908277541427497</v>
       </c>
       <c r="J47" t="n">
         <v>20</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>9.753999710083008</v>
+        <v>9.659999847412109</v>
       </c>
       <c r="I48" t="n">
-        <v>2.839860654431399</v>
+        <v>2.867494869311076</v>
       </c>
       <c r="J48" t="n">
         <v>20</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>3.006999969482422</v>
+        <v>3.009999990463257</v>
       </c>
       <c r="I50" t="n">
-        <v>3.658131064728068</v>
+        <v>3.654485061412586</v>
       </c>
       <c r="J50" t="n">
         <v>13</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>3.224999904632568</v>
+        <v>3.184999942779541</v>
       </c>
       <c r="I52" t="n">
-        <v>4.961240456787833</v>
+        <v>5.023547970941827</v>
       </c>
       <c r="J52" t="n">
         <v>6</v>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>0.9049999713897705</v>
+        <v>0.8999999761581421</v>
       </c>
       <c r="I53" t="n">
-        <v>2.762431026556669</v>
+        <v>2.777777851363761</v>
       </c>
       <c r="J53" t="n">
         <v>6</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>28.75</v>
+        <v>28.20000076293945</v>
       </c>
       <c r="I54" t="n">
-        <v>3.860869565217392</v>
+        <v>3.936170106274487</v>
       </c>
       <c r="J54" t="n">
         <v>2</v>
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>0.9039999842643738</v>
+        <v>0.8820000290870667</v>
       </c>
       <c r="I55" t="n">
-        <v>3.318584128561946</v>
+        <v>3.401360432045807</v>
       </c>
       <c r="J55" t="n">
         <v>-1</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>0.4995000064373016</v>
+        <v>0.4984999895095825</v>
       </c>
       <c r="I56" t="n">
-        <v>4.604604545262806</v>
+        <v>4.613841621667252</v>
       </c>
       <c r="J56" t="n">
         <v>-1</v>
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>19.79999923706055</v>
+        <v>20</v>
       </c>
       <c r="I57" t="n">
-        <v>3.030303147067567</v>
+        <v>3</v>
       </c>
       <c r="J57" t="n">
         <v>-1</v>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>9.520000457763672</v>
+        <v>9.380000114440918</v>
       </c>
       <c r="I58" t="n">
-        <v>2.100840235116771</v>
+        <v>2.132196136032998</v>
       </c>
       <c r="J58" t="n">
         <v>-1</v>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>2.319999933242798</v>
+        <v>2.289999961853027</v>
       </c>
       <c r="I59" t="n">
-        <v>7.75862091290682</v>
+        <v>7.860262139670395</v>
       </c>
       <c r="J59" t="n">
         <v>-8</v>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>8.449999809265137</v>
+        <v>8.5</v>
       </c>
       <c r="I60" t="n">
-        <v>3.55029593812606</v>
+        <v>3.529411764705882</v>
       </c>
       <c r="J60" t="n">
         <v>-8</v>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>15.96000003814697</v>
+        <v>16.14999961853027</v>
       </c>
       <c r="I61" t="n">
-        <v>1.566416036356264</v>
+        <v>1.547987652663184</v>
       </c>
       <c r="J61" t="n">
         <v>-8</v>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>3.849999904632568</v>
+        <v>3.859999895095825</v>
       </c>
       <c r="I62" t="n">
-        <v>0.7792207985226717</v>
+        <v>0.7772020936610736</v>
       </c>
       <c r="J62" t="n">
         <v>-8</v>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>4.150000095367432</v>
+        <v>4.130000114440918</v>
       </c>
       <c r="I63" t="n">
-        <v>3.614457748264686</v>
+        <v>3.631961158439475</v>
       </c>
       <c r="J63" t="n">
         <v>-8</v>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>12.85000038146973</v>
+        <v>12.89999961853027</v>
       </c>
       <c r="I64" t="n">
-        <v>4.513618543049896</v>
+        <v>4.496124163963973</v>
       </c>
       <c r="J64" t="n">
         <v>-8</v>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>2.226000070571899</v>
+        <v>2.220000028610229</v>
       </c>
       <c r="I65" t="n">
-        <v>4.672057354125803</v>
+        <v>4.684684624310854</v>
       </c>
       <c r="J65" t="n">
         <v>-15</v>
@@ -3531,10 +3531,10 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>10.93000030517578</v>
+        <v>10.9350004196167</v>
       </c>
       <c r="I66" t="n">
-        <v>2.65324786736441</v>
+        <v>2.652034649031731</v>
       </c>
       <c r="J66" t="n">
         <v>-15</v>
@@ -3578,10 +3578,10 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>2.119999885559082</v>
+        <v>2.105000019073486</v>
       </c>
       <c r="I67" t="n">
-        <v>3.632075667763242</v>
+        <v>3.65795721151069</v>
       </c>
       <c r="J67" t="n">
         <v>-15</v>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>38.88999938964844</v>
+        <v>39.11999893188477</v>
       </c>
       <c r="I68" t="n">
-        <v>4.217022436972647</v>
+        <v>4.192229153317582</v>
       </c>
       <c r="J68" t="n">
         <v>-15</v>
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>35.0099983215332</v>
+        <v>34.88999938964844</v>
       </c>
       <c r="I69" t="n">
-        <v>5.712653801442437</v>
+        <v>5.732301619338471</v>
       </c>
       <c r="J69" t="n">
         <v>-15</v>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>3.226000070571899</v>
+        <v>3.283999919891357</v>
       </c>
       <c r="I70" t="n">
-        <v>3.099813943347874</v>
+        <v>3.045067065754016</v>
       </c>
       <c r="J70" t="n">
         <v>-15</v>
@@ -3766,10 +3766,10 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>38.59000015258789</v>
+        <v>38.27000045776367</v>
       </c>
       <c r="I71" t="n">
-        <v>0.3847110635215795</v>
+        <v>0.3879278762064466</v>
       </c>
       <c r="J71" t="n">
         <v>-15</v>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>19.84000015258789</v>
+        <v>19.80999946594238</v>
       </c>
       <c r="I72" t="n">
-        <v>4.637096738529999</v>
+        <v>4.644119256952411</v>
       </c>
       <c r="J72" t="n">
         <v>-15</v>
@@ -3860,10 +3860,10 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>11.89000034332275</v>
+        <v>12.02999973297119</v>
       </c>
       <c r="I73" t="n">
-        <v>2.523128606707531</v>
+        <v>2.4937656413888</v>
       </c>
       <c r="J73" t="n">
         <v>-15</v>
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>82.59999847412109</v>
+        <v>83</v>
       </c>
       <c r="I74" t="n">
-        <v>1.259079926406822</v>
+        <v>1.253012048192771</v>
       </c>
       <c r="J74" t="n">
         <v>-15</v>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>44.59999847412109</v>
+        <v>44.66999816894531</v>
       </c>
       <c r="I75" t="n">
-        <v>1.569506780154199</v>
+        <v>1.567047299515319</v>
       </c>
       <c r="J75" t="n">
         <v>-15</v>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>55.20000076293945</v>
+        <v>54.54999923706055</v>
       </c>
       <c r="I76" t="n">
-        <v>3.985507191291655</v>
+        <v>4.032997306634881</v>
       </c>
       <c r="J76" t="n">
         <v>-15</v>
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>9.074999809265137</v>
+        <v>9.08899974822998</v>
       </c>
       <c r="I77" t="n">
-        <v>9.476584221213773</v>
+        <v>9.461987279375588</v>
       </c>
       <c r="J77" t="n">
         <v>-15</v>
@@ -4095,10 +4095,10 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>11.6560001373291</v>
+        <v>11.73999977111816</v>
       </c>
       <c r="I78" t="n">
-        <v>4.804392530904006</v>
+        <v>4.770017128770894</v>
       </c>
       <c r="J78" t="n">
         <v>-15</v>
@@ -4142,10 +4142,10 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>2.190000057220459</v>
+        <v>2.160000085830688</v>
       </c>
       <c r="I79" t="n">
-        <v>1.826483970542351</v>
+        <v>1.851851778265873</v>
       </c>
       <c r="J79" t="n">
         <v>-15</v>
@@ -4189,10 +4189,10 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>8.939999580383301</v>
+        <v>8.869999885559082</v>
       </c>
       <c r="I80" t="n">
-        <v>3.355704855493265</v>
+        <v>3.382187191325885</v>
       </c>
       <c r="J80" t="n">
         <v>-15</v>
@@ -4236,10 +4236,10 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>2.190000057220459</v>
+        <v>2.220000028610229</v>
       </c>
       <c r="I81" t="n">
-        <v>4.931506720464348</v>
+        <v>4.864864802168965</v>
       </c>
       <c r="J81" t="n">
         <v>-15</v>
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>88.69999694824219</v>
+        <v>90.30000305175781</v>
       </c>
       <c r="I82" t="n">
-        <v>2.322435254650619</v>
+        <v>2.28128452976824</v>
       </c>
       <c r="J82" t="n">
         <v>-15</v>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>15.35000038146973</v>
+        <v>15.22000026702881</v>
       </c>
       <c r="I83" t="n">
-        <v>4.88599336391801</v>
+        <v>4.927726588972079</v>
       </c>
       <c r="J83" t="n">
         <v>-15</v>
@@ -4377,10 +4377,10 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>14.21000003814697</v>
+        <v>14.13000011444092</v>
       </c>
       <c r="I84" t="n">
-        <v>2.111189297640008</v>
+        <v>2.123142233335149</v>
       </c>
       <c r="J84" t="n">
         <v>-15</v>
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>52.79999923706055</v>
+        <v>53.20000076293945</v>
       </c>
       <c r="I85" t="n">
-        <v>1.609848508110169</v>
+        <v>1.597744337989056</v>
       </c>
       <c r="J85" t="n">
         <v>-15</v>
@@ -4471,10 +4471,10 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>35.13999938964844</v>
+        <v>34.91999816894531</v>
       </c>
       <c r="I86" t="n">
-        <v>2.418895887204806</v>
+        <v>2.43413529372952</v>
       </c>
       <c r="J86" t="n">
         <v>-15</v>
@@ -4518,10 +4518,10 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>66.62000274658203</v>
+        <v>65.81999969482422</v>
       </c>
       <c r="I87" t="n">
-        <v>1.951365875719207</v>
+        <v>1.975083570385106</v>
       </c>
       <c r="J87" t="n">
         <v>-15</v>
@@ -4659,10 +4659,10 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>5.630000114440918</v>
+        <v>5.590000152587891</v>
       </c>
       <c r="I90" t="n">
-        <v>3.552397796351747</v>
+        <v>3.577817433643719</v>
       </c>
       <c r="J90" t="n">
         <v>-15</v>
@@ -4706,10 +4706,10 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>23.10000038146973</v>
+        <v>23.5</v>
       </c>
       <c r="I91" t="n">
-        <v>4.329004257515841</v>
+        <v>4.25531914893617</v>
       </c>
       <c r="J91" t="n">
         <v>-15</v>
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>4.789999961853027</v>
+        <v>4.730000019073486</v>
       </c>
       <c r="I92" t="n">
-        <v>4.488517781048719</v>
+        <v>4.545454527125229</v>
       </c>
       <c r="J92" t="n">
         <v>-15</v>
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>22.90999984741211</v>
+        <v>23.14500045776367</v>
       </c>
       <c r="I93" t="n">
-        <v>1.178524669569122</v>
+        <v>1.166558628904379</v>
       </c>
       <c r="J93" t="n">
         <v>-15</v>
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>9.5</v>
+        <v>9.439999580383301</v>
       </c>
       <c r="I94" t="n">
-        <v>2.105263157894737</v>
+        <v>2.118644161972296</v>
       </c>
       <c r="J94" t="n">
         <v>-15</v>
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>8.720000267028809</v>
+        <v>8.600000381469727</v>
       </c>
       <c r="I95" t="n">
-        <v>2.752293493699352</v>
+        <v>2.790697550631787</v>
       </c>
       <c r="J95" t="n">
         <v>-15</v>
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>20.78000068664551</v>
+        <v>20.57999992370605</v>
       </c>
       <c r="I96" t="n">
-        <v>3.801732309410856</v>
+        <v>3.838678342704952</v>
       </c>
       <c r="J96" t="n">
         <v>-15</v>
@@ -4988,10 +4988,10 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>5.260000228881836</v>
+        <v>5.239999771118164</v>
       </c>
       <c r="I97" t="n">
-        <v>1.768060759567112</v>
+        <v>1.774809237828549</v>
       </c>
       <c r="J97" t="n">
         <v>-15</v>
@@ -5035,10 +5035,10 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>7.25</v>
+        <v>7.300000190734863</v>
       </c>
       <c r="I98" t="n">
-        <v>0.8275862068965517</v>
+        <v>0.8219177867440579</v>
       </c>
       <c r="J98" t="n">
         <v>-15</v>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>34.91999816894531</v>
+        <v>35.09999847412109</v>
       </c>
       <c r="I99" t="n">
-        <v>1.00229100330039</v>
+        <v>0.9971510404994798</v>
       </c>
       <c r="J99" t="n">
         <v>-15</v>
@@ -5129,10 +5129,10 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>6.630000114440918</v>
+        <v>6.519999980926514</v>
       </c>
       <c r="I100" t="n">
-        <v>8.360482510289398</v>
+        <v>8.501533767201517</v>
       </c>
       <c r="J100" t="n">
         <v>-15</v>
@@ -5176,10 +5176,10 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>2.289999961853027</v>
+        <v>2.259999990463257</v>
       </c>
       <c r="I101" t="n">
-        <v>2.620087379890132</v>
+        <v>2.654867267840171</v>
       </c>
       <c r="J101" t="n">
         <v>-15</v>
@@ -5223,10 +5223,10 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>13.05000019073486</v>
+        <v>13.19999980926514</v>
       </c>
       <c r="I102" t="n">
-        <v>1.532567027408892</v>
+        <v>1.515151537044865</v>
       </c>
       <c r="J102" t="n">
         <v>-15</v>
@@ -5270,10 +5270,10 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>7.414999961853027</v>
+        <v>7.53000020980835</v>
       </c>
       <c r="I103" t="n">
-        <v>1.389076204044376</v>
+        <v>1.367861847677445</v>
       </c>
       <c r="J103" t="n">
         <v>-15</v>
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>5.75600004196167</v>
+        <v>5.75</v>
       </c>
       <c r="I104" t="n">
-        <v>3.300903381078628</v>
+        <v>3.304347826086956</v>
       </c>
       <c r="J104" t="n">
         <v>-15</v>
@@ -5364,10 +5364,10 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>9.939999580383301</v>
+        <v>9.814000129699707</v>
       </c>
       <c r="I105" t="n">
-        <v>4.346076642221965</v>
+        <v>4.401874814456707</v>
       </c>
       <c r="J105" t="n">
         <v>-15</v>
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>7.110000133514404</v>
+        <v>7.010000228881836</v>
       </c>
       <c r="I108" t="n">
-        <v>6.610407752097798</v>
+        <v>6.704707341713877</v>
       </c>
       <c r="J108" t="n">
         <v>-15</v>
@@ -5552,10 +5552,10 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>55.61999893188477</v>
+        <v>54.95999908447266</v>
       </c>
       <c r="I109" t="n">
-        <v>2.517080235320599</v>
+        <v>2.547307174893183</v>
       </c>
       <c r="J109" t="n">
         <v>-15</v>
@@ -5599,10 +5599,10 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>3.51200008392334</v>
+        <v>3.469000101089478</v>
       </c>
       <c r="I110" t="n">
-        <v>8.542141025943906</v>
+        <v>8.648025115530602</v>
       </c>
       <c r="J110" t="n">
         <v>-15</v>
@@ -5646,10 +5646,10 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>15.80000019073486</v>
+        <v>15.94999980926514</v>
       </c>
       <c r="I111" t="n">
-        <v>0.7594936617175999</v>
+        <v>0.7523511061755226</v>
       </c>
       <c r="J111" t="n">
         <v>-15</v>
@@ -5693,10 +5693,10 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>3.450000047683716</v>
+        <v>3.420000076293945</v>
       </c>
       <c r="I112" t="n">
-        <v>4.927536163778773</v>
+        <v>4.970760123029561</v>
       </c>
       <c r="J112" t="n">
         <v>-15</v>
@@ -5740,10 +5740,10 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>22.64999961853027</v>
+        <v>22.39999961853027</v>
       </c>
       <c r="I113" t="n">
-        <v>3.090507778319433</v>
+        <v>3.125000053218434</v>
       </c>
       <c r="J113" t="n">
         <v>-15</v>
@@ -5787,10 +5787,10 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>2.400000095367432</v>
+        <v>2.440000057220459</v>
       </c>
       <c r="I114" t="n">
-        <v>1.458333275384376</v>
+        <v>1.434426195869457</v>
       </c>
       <c r="J114" t="n">
         <v>-15</v>
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>5.550000190734863</v>
+        <v>5.539999961853027</v>
       </c>
       <c r="I115" t="n">
-        <v>5.945945741603757</v>
+        <v>5.956678741377123</v>
       </c>
       <c r="J115" t="n">
         <v>-15</v>
@@ -5881,10 +5881,10 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>0.8880000114440918</v>
+        <v>0.878000020980835</v>
       </c>
       <c r="I116" t="n">
-        <v>7.882882781292305</v>
+        <v>7.972664957547646</v>
       </c>
       <c r="J116" t="n">
         <v>-15</v>
@@ -5928,10 +5928,10 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>51</v>
+        <v>50.70000076293945</v>
       </c>
       <c r="I117" t="n">
-        <v>1.392156862745098</v>
+        <v>1.400394456244257</v>
       </c>
       <c r="J117" t="n">
         <v>-15</v>
@@ -5975,10 +5975,10 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>109.6999969482422</v>
+        <v>107.3000030517578</v>
       </c>
       <c r="I118" t="n">
-        <v>1.230629022384519</v>
+        <v>1.25815467064694</v>
       </c>
       <c r="J118" t="n">
         <v>-15</v>
@@ -6022,10 +6022,10 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>7.820000171661377</v>
+        <v>8.100000381469727</v>
       </c>
       <c r="I119" t="n">
-        <v>1.023017880356438</v>
+        <v>0.9876542744740486</v>
       </c>
       <c r="J119" t="n">
         <v>-15</v>
@@ -6116,10 +6116,10 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>4.269000053405762</v>
+        <v>4.328999996185303</v>
       </c>
       <c r="I121" t="n">
-        <v>3.982197186068805</v>
+        <v>3.927003930464387</v>
       </c>
       <c r="J121" t="n">
         <v>-15</v>
@@ -6210,10 +6210,10 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>56.5</v>
+        <v>56.20000076293945</v>
       </c>
       <c r="I123" t="n">
-        <v>0.7964601769911505</v>
+        <v>0.800711732902232</v>
       </c>
       <c r="J123" t="n">
         <v>-15</v>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>5.900000095367432</v>
+        <v>5.820000171661377</v>
       </c>
       <c r="I124" t="n">
-        <v>0.6779660907362907</v>
+        <v>0.6872852030961643</v>
       </c>
       <c r="J124" t="n">
         <v>-15</v>
@@ -6304,10 +6304,10 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>38.34000015258789</v>
+        <v>38.27999877929688</v>
       </c>
       <c r="I125" t="n">
-        <v>2.738654136205387</v>
+        <v>2.742946795933222</v>
       </c>
       <c r="J125" t="n">
         <v>-15</v>
@@ -6398,10 +6398,10 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>17.60000038146973</v>
+        <v>17.51000022888184</v>
       </c>
       <c r="I127" t="n">
-        <v>2.159090862293875</v>
+        <v>2.170188435367406</v>
       </c>
       <c r="J127" t="n">
         <v>-15</v>
@@ -6445,10 +6445,10 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>26.93000030517578</v>
+        <v>27.48999977111816</v>
       </c>
       <c r="I128" t="n">
-        <v>2.227998489419563</v>
+        <v>2.182611877030201</v>
       </c>
       <c r="J128" t="n">
         <v>-15</v>
@@ -6492,10 +6492,10 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>37.70000076293945</v>
+        <v>36.84999847412109</v>
       </c>
       <c r="I129" t="n">
-        <v>0.9283819440769439</v>
+        <v>0.9497965115135539</v>
       </c>
       <c r="J129" t="n">
         <v>-15</v>
@@ -6586,10 +6586,10 @@
         </is>
       </c>
       <c r="H131" t="n">
-        <v>2.914999961853027</v>
+        <v>2.934999942779541</v>
       </c>
       <c r="I131" t="n">
-        <v>0.3430531777311973</v>
+        <v>0.3407155091979209</v>
       </c>
       <c r="J131" t="n">
         <v>-15</v>
@@ -6633,10 +6633,10 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>20.92000007629395</v>
+        <v>20.88999938964844</v>
       </c>
       <c r="I132" t="n">
-        <v>5.353728469959031</v>
+        <v>5.361417102553821</v>
       </c>
       <c r="J132" t="n">
         <v>-15</v>
@@ -6680,10 +6680,10 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>1.379999995231628</v>
+        <v>1.399999976158142</v>
       </c>
       <c r="I133" t="n">
-        <v>7.246376836632912</v>
+        <v>7.142857264499278</v>
       </c>
       <c r="J133" t="n">
         <v>-15</v>
@@ -6727,10 +6727,10 @@
         </is>
       </c>
       <c r="H134" t="n">
-        <v>9.119999885559082</v>
+        <v>9.079999923706055</v>
       </c>
       <c r="I134" t="n">
-        <v>2.850877228756251</v>
+        <v>2.863436147407802</v>
       </c>
       <c r="J134" t="n">
         <v>-15</v>
@@ -6774,10 +6774,10 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>2.220000028610229</v>
+        <v>2.151999950408936</v>
       </c>
       <c r="I135" t="n">
-        <v>4.157657604075883</v>
+        <v>4.28903355608631</v>
       </c>
       <c r="J135" t="n">
         <v>-15</v>
@@ -6821,10 +6821,10 @@
         </is>
       </c>
       <c r="H136" t="n">
-        <v>9.140000343322754</v>
+        <v>9.239999771118164</v>
       </c>
       <c r="I136" t="n">
-        <v>3.829321519180174</v>
+        <v>3.787878881707432</v>
       </c>
       <c r="J136" t="n">
         <v>-22</v>
@@ -6868,10 +6868,10 @@
         </is>
       </c>
       <c r="H137" t="n">
-        <v>5.75</v>
+        <v>6.449999809265137</v>
       </c>
       <c r="I137" t="n">
-        <v>1.669565217391304</v>
+        <v>1.48837213703635</v>
       </c>
       <c r="J137" t="n">
         <v>-22</v>
@@ -6915,10 +6915,10 @@
         </is>
       </c>
       <c r="H138" t="n">
-        <v>6.25</v>
+        <v>6.449999809265137</v>
       </c>
       <c r="I138" t="n">
-        <v>4.8</v>
+        <v>4.651162928238593</v>
       </c>
       <c r="J138" t="n">
         <v>-22</v>
@@ -6962,10 +6962,10 @@
         </is>
       </c>
       <c r="H139" t="n">
-        <v>11.60000038146973</v>
+        <v>11.39999961853027</v>
       </c>
       <c r="I139" t="n">
-        <v>1.724137874335655</v>
+        <v>1.754386023617996</v>
       </c>
       <c r="J139" t="n">
         <v>-22</v>
@@ -7009,10 +7009,10 @@
         </is>
       </c>
       <c r="H140" t="n">
-        <v>9.100000381469727</v>
+        <v>9.260000228881836</v>
       </c>
       <c r="I140" t="n">
-        <v>0.6593406317012648</v>
+        <v>0.6479481481313648</v>
       </c>
       <c r="J140" t="n">
         <v>-22</v>
@@ -7056,10 +7056,10 @@
         </is>
       </c>
       <c r="H141" t="n">
-        <v>18.70000076293945</v>
+        <v>18.63999938964844</v>
       </c>
       <c r="I141" t="n">
-        <v>2.673796682355883</v>
+        <v>2.682403521309506</v>
       </c>
       <c r="J141" t="n">
         <v>-22</v>
@@ -7103,10 +7103,10 @@
         </is>
       </c>
       <c r="H142" t="n">
-        <v>2.359999895095825</v>
+        <v>2.319999933242798</v>
       </c>
       <c r="I142" t="n">
-        <v>2.542372994366755</v>
+        <v>2.58620697096894</v>
       </c>
       <c r="J142" t="n">
         <v>-22</v>
@@ -7150,10 +7150,10 @@
         </is>
       </c>
       <c r="H143" t="n">
-        <v>15.47999954223633</v>
+        <v>15.35999965667725</v>
       </c>
       <c r="I143" t="n">
-        <v>3.229974255721245</v>
+        <v>3.255208406092911</v>
       </c>
       <c r="J143" t="n">
         <v>-22</v>
@@ -7244,10 +7244,10 @@
         </is>
       </c>
       <c r="H145" t="n">
-        <v>3.230000019073486</v>
+        <v>3.25</v>
       </c>
       <c r="I145" t="n">
-        <v>3.405572735307695</v>
+        <v>3.384615384615385</v>
       </c>
       <c r="J145" t="n">
         <v>-22</v>
@@ -7291,10 +7291,10 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>8.699999809265137</v>
+        <v>8.550000190734863</v>
       </c>
       <c r="I146" t="n">
-        <v>0.9770115156724321</v>
+        <v>0.9941520246059123</v>
       </c>
       <c r="J146" t="n">
         <v>-22</v>
@@ -7338,10 +7338,10 @@
         </is>
       </c>
       <c r="H147" t="n">
-        <v>4.760000228881836</v>
+        <v>4.889999866485596</v>
       </c>
       <c r="I147" t="n">
-        <v>1.995798223360933</v>
+        <v>1.942740339342294</v>
       </c>
       <c r="J147" t="n">
         <v>-22</v>
@@ -7385,10 +7385,10 @@
         </is>
       </c>
       <c r="H148" t="n">
-        <v>1.289999961853027</v>
+        <v>1.279999971389771</v>
       </c>
       <c r="I148" t="n">
-        <v>2.325581464119296</v>
+        <v>2.343750052386896</v>
       </c>
       <c r="J148" t="n">
         <v>-22</v>
@@ -7432,10 +7432,10 @@
         </is>
       </c>
       <c r="H149" t="n">
-        <v>8</v>
+        <v>8.149999618530273</v>
       </c>
       <c r="I149" t="n">
-        <v>1.125</v>
+        <v>1.104294530215329</v>
       </c>
       <c r="J149" t="n">
         <v>-22</v>
@@ -7526,10 +7526,10 @@
         </is>
       </c>
       <c r="H151" t="n">
-        <v>7.179999828338623</v>
+        <v>7.119999885559082</v>
       </c>
       <c r="I151" t="n">
-        <v>3.064066925624227</v>
+        <v>3.089887690113706</v>
       </c>
       <c r="J151" t="n">
         <v>-22</v>
@@ -7573,10 +7573,10 @@
         </is>
       </c>
       <c r="H152" t="n">
-        <v>24.35000038146973</v>
+        <v>25.39999961853027</v>
       </c>
       <c r="I152" t="n">
-        <v>2.505133430980182</v>
+        <v>2.401574839217642</v>
       </c>
       <c r="J152" t="n">
         <v>-29</v>
@@ -7620,10 +7620,10 @@
         </is>
       </c>
       <c r="H153" t="n">
-        <v>2.779999971389771</v>
+        <v>2.819999933242798</v>
       </c>
       <c r="I153" t="n">
-        <v>5.395683508766814</v>
+        <v>5.319149062089187</v>
       </c>
       <c r="J153" t="n">
         <v>-29</v>
@@ -7667,10 +7667,10 @@
         </is>
       </c>
       <c r="H154" t="n">
-        <v>11.25</v>
+        <v>11</v>
       </c>
       <c r="I154" t="n">
-        <v>6.222222222222222</v>
+        <v>6.363636363636363</v>
       </c>
       <c r="J154" t="n">
         <v>-29</v>
@@ -7761,10 +7761,10 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>7.239999771118164</v>
+        <v>7.09499979019165</v>
       </c>
       <c r="I156" t="n">
-        <v>3.729281885851504</v>
+        <v>3.805496941286122</v>
       </c>
       <c r="J156" t="n">
         <v>-29</v>
@@ -7808,10 +7808,10 @@
         </is>
       </c>
       <c r="H157" t="n">
-        <v>7.550000190734863</v>
+        <v>7.460000038146973</v>
       </c>
       <c r="I157" t="n">
-        <v>4.635761472291215</v>
+        <v>4.691688984051778</v>
       </c>
       <c r="J157" t="n">
         <v>-29</v>
@@ -7855,10 +7855,10 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>43.59999847412109</v>
+        <v>43.20000076293945</v>
       </c>
       <c r="I158" t="n">
-        <v>2.522935868112262</v>
+        <v>2.546296251327087</v>
       </c>
       <c r="J158" t="n">
         <v>-29</v>
@@ -7949,10 +7949,10 @@
         </is>
       </c>
       <c r="H160" t="n">
-        <v>11.35000038146973</v>
+        <v>11.25</v>
       </c>
       <c r="I160" t="n">
-        <v>3.788546128174832</v>
+        <v>3.822222222222222</v>
       </c>
       <c r="J160" t="n">
         <v>-29</v>
@@ -7996,10 +7996,10 @@
         </is>
       </c>
       <c r="H161" t="n">
-        <v>4.389999866485596</v>
+        <v>4.375</v>
       </c>
       <c r="I161" t="n">
-        <v>3.416856595945233</v>
+        <v>3.428571428571429</v>
       </c>
       <c r="J161" t="n">
         <v>-29</v>
@@ -8043,10 +8043,10 @@
         </is>
       </c>
       <c r="H162" t="n">
-        <v>11.9399995803833</v>
+        <v>11.81999969482422</v>
       </c>
       <c r="I162" t="n">
-        <v>1.651331716325491</v>
+        <v>1.668096489768414</v>
       </c>
       <c r="J162" t="n">
         <v>-29</v>
@@ -8090,10 +8090,10 @@
         </is>
       </c>
       <c r="H163" t="n">
-        <v>28.14999961853027</v>
+        <v>27.79999923706055</v>
       </c>
       <c r="I163" t="n">
-        <v>3.907637708371066</v>
+        <v>3.956834640964937</v>
       </c>
       <c r="J163" t="n">
         <v>-29</v>
@@ -8137,10 +8137,10 @@
         </is>
       </c>
       <c r="H164" t="n">
-        <v>68.59999847412109</v>
+        <v>71.30000305175781</v>
       </c>
       <c r="I164" t="n">
-        <v>0.6851312105747415</v>
+        <v>0.6591865075501041</v>
       </c>
       <c r="J164" t="n">
         <v>-29</v>
@@ -8184,10 +8184,10 @@
         </is>
       </c>
       <c r="H165" t="n">
-        <v>88.69999694824219</v>
+        <v>88.40000152587891</v>
       </c>
       <c r="I165" t="n">
-        <v>1.35287490562172</v>
+        <v>1.357466039917095</v>
       </c>
       <c r="J165" t="n">
         <v>-29</v>
@@ -8231,10 +8231,10 @@
         </is>
       </c>
       <c r="H166" t="n">
-        <v>22.25</v>
+        <v>21.95000076293945</v>
       </c>
       <c r="I166" t="n">
-        <v>1.213483146067416</v>
+        <v>1.230068294375051</v>
       </c>
       <c r="J166" t="n">
         <v>-29</v>
@@ -8278,10 +8278,10 @@
         </is>
       </c>
       <c r="H167" t="n">
-        <v>10.35000038146973</v>
+        <v>10.30000019073486</v>
       </c>
       <c r="I167" t="n">
-        <v>3.671497449220761</v>
+        <v>3.689320320030873</v>
       </c>
       <c r="J167" t="n">
         <v>-29</v>
@@ -8325,10 +8325,10 @@
         </is>
       </c>
       <c r="H168" t="n">
-        <v>35.54999923706055</v>
+        <v>35</v>
       </c>
       <c r="I168" t="n">
-        <v>0.8438818746506547</v>
+        <v>0.8571428571428572</v>
       </c>
       <c r="J168" t="n">
         <v>-29</v>
@@ -10330,95 +10330,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>E-Globe S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>OPS Italia S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>OSAI Automation System S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Half Year Preliminary Results</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>